--- a/models/builds/2026-05-17-nguyen-coca-cola-financials.xlsx
+++ b/models/builds/2026-05-17-nguyen-coca-cola-financials.xlsx
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="C15" s="95" t="n">
-        <v>21561</v>
+        <v>24856</v>
       </c>
       <c r="D15" s="88" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="C19" s="95" t="n">
-        <v>63936</v>
+        <v>67231</v>
       </c>
       <c r="D19" s="88" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         </is>
       </c>
       <c r="C36" s="96" t="n">
-        <v>26865</v>
+        <v>28512.5</v>
       </c>
       <c r="D36" s="88" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         </is>
       </c>
       <c r="C38" s="96" t="n">
-        <v>69112</v>
+        <v>70759.5</v>
       </c>
       <c r="D38" s="88" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="C45" s="97" t="n">
-        <v>8741.024800000001</v>
+        <v>8444.4748</v>
       </c>
       <c r="D45" s="88" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="C48" s="99" t="n">
-        <v>0.2267152277277277</v>
+        <v>0.2156038851125225</v>
       </c>
       <c r="D48" s="88" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         </is>
       </c>
       <c r="C49" s="99" t="n">
-        <v>0.6092945596215389</v>
+        <v>0.5285242999678146</v>
       </c>
       <c r="D49" s="88" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="C51" s="99" t="n">
-        <v>0.2097358606320176</v>
+        <v>0.2048525611402003</v>
       </c>
       <c r="D51" s="88" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="C52" s="99" t="n">
-        <v>0.489000558347292</v>
+        <v>0.4607452871547567</v>
       </c>
       <c r="D52" s="88" t="inlineStr">
         <is>
